--- a/data/availability/projects/mountain-view/mountain-view-mv4.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-mv4.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fact sheet inventory for mountain-view-mv4</t>
+          <t>Inventory for mountain-view-mv4</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,45 +554,145 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Town House</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="H2" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" t="n">
-        <v>197</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Fully Finished</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>12 month</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Over 7 Years</t>
+      <c r="E3" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="H3" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>EARLY DELIVERY - 12</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Villa</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="H4" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
         </is>
       </c>
     </row>
@@ -607,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,12 +785,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Town House</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MV4-THM</t>
+          <t>MV4-A-TH-001-2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -703,11 +803,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>197</v>
+        <v>59.49</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
@@ -716,19 +816,931 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>27001934</v>
+        <v>25429896</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12 month</t>
+          <t>READY TO MOVE - 6</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Over 7 Years</t>
+          <t>5%+5% DP over 8 years</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-001-3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>25432900</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-001-4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>25636898</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-001-5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>25636898</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-002-3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>25637725</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-002-4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>26045173</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-008-4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>25917673</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>EARLY DELIVERY - 12</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-135-3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>23307369</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-135-4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>23310885</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-136-4</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>62.36</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>23390909</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-139-2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>23930454</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-139-4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>84.08</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>23853875</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Town House</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MV4-A-TH-139-5</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>82.17</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>23812652</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Villa</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MV4-A-VA-004-0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>41329140</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Villa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MV4-A-VB-130-0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>36586610</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Villa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MV4-A-VB-131-0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>37165685</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Villa</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MV4-A-VC-127-0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>34707385</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>READY TO MOVE - 6</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5%+5% DP over 8 years</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>Available</t>
         </is>

--- a/data/availability/projects/mountain-view/mountain-view-mv4.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-mv4.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for mountain-view-mv4</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -809,7 +819,6 @@
       <c r="G2" t="n">
         <v>59.49</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -866,7 +875,6 @@
       <c r="G3" t="n">
         <v>59.59</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -923,7 +931,6 @@
       <c r="G4" t="n">
         <v>59.59</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -980,7 +987,6 @@
       <c r="G5" t="n">
         <v>59.59</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1037,7 +1043,6 @@
       <c r="G6" t="n">
         <v>59.59</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1094,7 +1099,6 @@
       <c r="G7" t="n">
         <v>59.59</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1151,7 +1155,6 @@
       <c r="G8" t="n">
         <v>59.6</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1208,7 +1211,6 @@
       <c r="G9" t="n">
         <v>57.6</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1265,7 +1267,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1322,7 +1323,6 @@
       <c r="G11" t="n">
         <v>62.36</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1379,7 +1379,6 @@
       <c r="G12" t="n">
         <v>98.53</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1436,7 +1435,6 @@
       <c r="G13" t="n">
         <v>84.08</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1493,7 +1491,6 @@
       <c r="G14" t="n">
         <v>82.17</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1550,7 +1547,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1607,7 +1603,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1664,7 +1659,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1721,7 +1715,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/mountain-view/mountain-view-mv4.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-mv4.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
